--- a/ArduinoIDE/AStar/array.xlsx
+++ b/ArduinoIDE/AStar/array.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Maker\ArduinoSample\ArduinoIDE\AStar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676908DB-277E-48A7-8228-9FCA19EAAE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4470" yWindow="2415" windowWidth="7650" windowHeight="6390" xr2:uid="{9685873A-3842-4DE5-B907-2AEE82AB4B3A}"/>
+    <workbookView xWindow="4476" yWindow="2412" windowWidth="7656" windowHeight="6396"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,9 +32,39 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+  <si>
+    <t>(0,0)</t>
+  </si>
+  <si>
+    <t>(2,0)</t>
+  </si>
+  <si>
+    <t>(3,5)</t>
+  </si>
+  <si>
+    <t>倉庫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>充電</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>客戶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -51,8 +80,16 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="王漢宗波卡體一空陰"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -68,6 +105,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -101,7 +162,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -114,11 +175,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -427,16 +514,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53B17279-6E5D-4779-8782-0F40C5E7C677}">
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
-    <col min="2" max="6" width="5.625" customWidth="1"/>
-    <col min="8" max="16" width="5.625" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" customWidth="1"/>
+    <col min="2" max="6" width="5.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="16" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B1">
         <v>0</v>
       </c>
@@ -477,7 +565,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -537,7 +625,7 @@
         <v>(0,7)</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -597,7 +685,7 @@
         <v>(1,7)</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -657,7 +745,7 @@
         <v>(2,7)</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -717,7 +805,7 @@
         <v>(3,7)</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -777,7 +865,7 @@
         <v>(4,7)</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H7">
         <v>5</v>
       </c>
@@ -814,7 +902,7 @@
         <v>(5,7)</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H8">
         <v>6</v>
       </c>
@@ -851,7 +939,7 @@
         <v>(6,7)</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H9">
         <v>7</v>
       </c>
@@ -888,8 +976,297 @@
         <v>(7,7)</v>
       </c>
     </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>3</v>
+      </c>
+      <c r="N11">
+        <v>4</v>
+      </c>
+      <c r="O11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f>"("&amp;$A12&amp;","&amp;I$1&amp;")"</f>
+        <v>(0,0)</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <f>"("&amp;$A12&amp;","&amp;J$1&amp;")"</f>
+        <v>(0,1)</v>
+      </c>
+      <c r="D12" s="3" t="str">
+        <f>"("&amp;$A12&amp;","&amp;K$1&amp;")"</f>
+        <v>(0,2)</v>
+      </c>
+      <c r="E12" s="4" t="str">
+        <f>"("&amp;$A12&amp;","&amp;L$1&amp;")"</f>
+        <v>(0,3)</v>
+      </c>
+      <c r="F12" s="4" t="str">
+        <f>"("&amp;$A12&amp;","&amp;M$1&amp;")"</f>
+        <v>(0,4)</v>
+      </c>
+      <c r="G12" s="4" t="str">
+        <f>"("&amp;$A12&amp;","&amp;N$1&amp;")"</f>
+        <v>(0,5)</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="str">
+        <f>"{"&amp;J12&amp;","&amp;K12&amp;","&amp;L12&amp;","&amp;M12&amp;","&amp;N12&amp;","&amp;O12&amp;"},"</f>
+        <v>{1,1,0,1,1,1},</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="str">
+        <f>"("&amp;$A13&amp;","&amp;I$1&amp;")"</f>
+        <v>(1,0)</v>
+      </c>
+      <c r="C13" s="3" t="str">
+        <f>"("&amp;$A13&amp;","&amp;J$1&amp;")"</f>
+        <v>(1,1)</v>
+      </c>
+      <c r="D13" s="3" t="str">
+        <f>"("&amp;$A13&amp;","&amp;K$1&amp;")"</f>
+        <v>(1,2)</v>
+      </c>
+      <c r="E13" s="4" t="str">
+        <f>"("&amp;$A13&amp;","&amp;L$1&amp;")"</f>
+        <v>(1,3)</v>
+      </c>
+      <c r="F13" s="3" t="str">
+        <f>"("&amp;$A13&amp;","&amp;M$1&amp;")"</f>
+        <v>(1,4)</v>
+      </c>
+      <c r="G13" s="4" t="str">
+        <f>"("&amp;$A13&amp;","&amp;N$1&amp;")"</f>
+        <v>(1,5)</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" ref="Q13:Q15" si="4">"{"&amp;J13&amp;","&amp;K13&amp;","&amp;L13&amp;","&amp;M13&amp;","&amp;N13&amp;","&amp;O13&amp;"},"</f>
+        <v>{1,0,0,1,0,1},</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="18" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" s="7" t="str">
+        <f>"("&amp;$A14&amp;","&amp;I$1&amp;")"</f>
+        <v>(2,0)</v>
+      </c>
+      <c r="C14" s="3" t="str">
+        <f>"("&amp;$A14&amp;","&amp;J$1&amp;")"</f>
+        <v>(2,1)</v>
+      </c>
+      <c r="D14" s="4" t="str">
+        <f>"("&amp;$A14&amp;","&amp;K$1&amp;")"</f>
+        <v>(2,2)</v>
+      </c>
+      <c r="E14" s="4" t="str">
+        <f>"("&amp;$A14&amp;","&amp;L$1&amp;")"</f>
+        <v>(2,3)</v>
+      </c>
+      <c r="F14" s="3" t="str">
+        <f>"("&amp;$A14&amp;","&amp;M$1&amp;")"</f>
+        <v>(2,4)</v>
+      </c>
+      <c r="G14" s="4" t="str">
+        <f>"("&amp;$A14&amp;","&amp;N$1&amp;")"</f>
+        <v>(2,5)</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="4"/>
+        <v>{1,0,1,1,0,1},</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>3</v>
+      </c>
+      <c r="B15" s="4" t="str">
+        <f>"("&amp;$A15&amp;","&amp;I$1&amp;")"</f>
+        <v>(3,0)</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f>"("&amp;$A15&amp;","&amp;J$1&amp;")"</f>
+        <v>(3,1)</v>
+      </c>
+      <c r="D15" s="4" t="str">
+        <f>"("&amp;$A15&amp;","&amp;K$1&amp;")"</f>
+        <v>(3,2)</v>
+      </c>
+      <c r="E15" s="3" t="str">
+        <f>"("&amp;$A15&amp;","&amp;L$1&amp;")"</f>
+        <v>(3,3)</v>
+      </c>
+      <c r="F15" s="3" t="str">
+        <f>"("&amp;$A15&amp;","&amp;M$1&amp;")"</f>
+        <v>(3,4)</v>
+      </c>
+      <c r="G15" s="6" t="str">
+        <f>"("&amp;$A15&amp;","&amp;N$1&amp;")"</f>
+        <v>(3,5)</v>
+      </c>
+      <c r="I15">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="str">
+        <f>"{"&amp;J15&amp;","&amp;K15&amp;","&amp;L15&amp;","&amp;M15&amp;","&amp;N15&amp;","&amp;O15&amp;"}"</f>
+        <v>{1,1,1,0,0,1}</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="J12:O15">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
